--- a/su25fungv3.xlsx
+++ b/su25fungv3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EF8FEDD-A7D8-48AD-9F6E-9F959FD409F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48351CB1-47C6-49B9-84E9-AD2141966556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B92E0137-6717-430D-BC87-94BB95C29D48}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
   <si>
     <t>Treatment</t>
   </si>
@@ -45,39 +45,6 @@
   </si>
   <si>
     <t>Treatment_sum</t>
-  </si>
-  <si>
-    <t>Week 1</t>
-  </si>
-  <si>
-    <t>Week 2</t>
-  </si>
-  <si>
-    <t>Week 3</t>
-  </si>
-  <si>
-    <t>Week 4</t>
-  </si>
-  <si>
-    <t>Week 5</t>
-  </si>
-  <si>
-    <t>Week 6</t>
-  </si>
-  <si>
-    <t>Week 7</t>
-  </si>
-  <si>
-    <t>Week 8</t>
-  </si>
-  <si>
-    <t>Week 9</t>
-  </si>
-  <si>
-    <t>Week 10</t>
-  </si>
-  <si>
-    <t>Week 11</t>
   </si>
   <si>
     <t>C</t>
@@ -471,10 +438,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -482,10 +449,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3">
         <v>15</v>
@@ -493,10 +460,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -504,10 +471,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -515,10 +482,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -526,10 +493,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -537,10 +504,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
       </c>
       <c r="C8">
         <v>16</v>
@@ -548,10 +515,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -559,10 +526,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
       </c>
       <c r="C10">
         <v>19</v>
@@ -570,10 +537,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
       </c>
       <c r="C11">
         <v>21</v>
@@ -581,10 +548,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
       </c>
       <c r="C12">
         <v>24</v>
@@ -592,10 +559,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -603,10 +570,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
       </c>
       <c r="C14">
         <v>24</v>
@@ -614,10 +581,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
       </c>
       <c r="C15">
         <v>26</v>
@@ -625,10 +592,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
       </c>
       <c r="C16">
         <v>24</v>
@@ -636,10 +603,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
       </c>
       <c r="C17">
         <v>27</v>
@@ -647,10 +614,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
       </c>
       <c r="C18">
         <v>24</v>
@@ -658,10 +625,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
       </c>
       <c r="C19">
         <v>27</v>
@@ -669,10 +636,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
       </c>
       <c r="C20">
         <v>24</v>
@@ -680,10 +647,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
       </c>
       <c r="C21">
         <v>27</v>
@@ -691,10 +658,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>11</v>
       </c>
       <c r="C22">
         <v>24</v>
@@ -702,10 +669,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>11</v>
       </c>
       <c r="C23">
         <v>27</v>
